--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_287_R29.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_287_R29.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8235</v>
+        <v>4.6623</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7724</v>
+        <v>5.6112</v>
       </c>
       <c r="F2" t="n">
         <v>-0.949</v>
@@ -610,10 +610,10 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1731</v>
+        <v>-0.3343</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2513</v>
+        <v>-0.4125</v>
       </c>
       <c r="U2" t="n">
         <v>0.07820000000000001</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.769</v>
+        <v>2.4918</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7446</v>
+        <v>1.1732</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0244</v>
+        <v>1.3186</v>
       </c>
       <c r="G3" t="n">
         <v>-0.8649</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.402</v>
+        <v>0.1248</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8136</v>
+        <v>-0.3851</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2156</v>
+        <v>0.5098</v>
       </c>
       <c r="V3" t="n">
         <v>1.6083</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7607</v>
+        <v>2.3368</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9137</v>
+        <v>1.3554</v>
       </c>
       <c r="F4" t="n">
-        <v>0.847</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>3.1401</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.449</v>
+        <v>-0.8729</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0791</v>
+        <v>-0.4793</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.528</v>
+        <v>-0.3936</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3943</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. BACON</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6968</v>
+        <v>1.9358</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8699</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.827</v>
+        <v>1.0401</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7198</v>
+        <v>3.1555</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4631</v>
+        <v>2.7874</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.7433</v>
+        <v>0.368</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9229000000000001</v>
+        <v>3.9632</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0305</v>
+        <v>1.8051</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1077</v>
+        <v>2.1581</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7969000000000001</v>
+        <v>-0.8077</v>
       </c>
       <c r="N5" t="n">
-        <v>1.4325</v>
+        <v>0.9823</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-1.79</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R5" t="n">
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0952</v>
+        <v>-0.4542</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0376</v>
+        <v>-0.3536</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0575</v>
+        <v>-0.1006</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>0.3943</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1444</v>
+        <v>-0.3943</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>D. BACON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4236</v>
+        <v>1.8827</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5851</v>
+        <v>1.2238</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8384</v>
+        <v>0.6589</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1555</v>
+        <v>1.7198</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7874</v>
+        <v>3.4631</v>
       </c>
       <c r="I6" t="n">
-        <v>0.368</v>
+        <v>-1.7433</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9632</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8051</v>
+        <v>2.0305</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1581</v>
+        <v>-1.1077</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8077</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.9823</v>
+        <v>1.4325</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.79</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-1.1598</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9665</v>
+        <v>-0.9093</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6642</v>
+        <v>-0.6838</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3022</v>
+        <v>-0.2256</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3943</v>
+        <v>2.1444</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7886</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. DANGUBIC</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4719</v>
+        <v>1.0318</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2889</v>
+        <v>1.122</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1829</v>
+        <v>-0.0902</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0856</v>
+        <v>2.0369</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2065</v>
+        <v>0.9293</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1209</v>
+        <v>1.1075</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1747</v>
+        <v>1.7508</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9243</v>
+        <v>0.2185</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7495000000000001</v>
+        <v>1.5324</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0891</v>
+        <v>0.2861</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2822</v>
+        <v>0.7109</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3713</v>
+        <v>-0.4248</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2987</v>
+        <v>-1.1854</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1142</v>
+        <v>-0.6289</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1845</v>
+        <v>-0.5566</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4636</v>
+        <v>0.8414</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2306</v>
+        <v>0.08</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6942</v>
+        <v>0.7614</v>
       </c>
       <c r="G8" t="n">
         <v>0.9086</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3548</v>
+        <v>-0.977</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8215</v>
+        <v>-0.5109</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5333</v>
+        <v>-0.4661</v>
       </c>
       <c r="V8" t="n">
         <v>0.6778999999999999</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>N. DANGUBIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3686</v>
+        <v>-0.0254</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9293</v>
+        <v>0.1277</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5607</v>
+        <v>-0.1531</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0369</v>
+        <v>0.0856</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9293</v>
+        <v>1.2065</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1075</v>
+        <v>-1.1209</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7508</v>
+        <v>0.1747</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2185</v>
+        <v>0.9243</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5324</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2861</v>
+        <v>-0.0891</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7109</v>
+        <v>0.2822</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4248</v>
+        <v>-0.3713</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8486</v>
+        <v>-0.1986</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8215</v>
+        <v>-0.047</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0271</v>
+        <v>-0.1516</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.98</v>
+        <v>-1.3099</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4315</v>
+        <v>-0.8286</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5485</v>
+        <v>-0.4813</v>
       </c>
       <c r="G10" t="n">
         <v>0.0291</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3286</v>
+        <v>-0.6585</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0351</v>
+        <v>-0.4323</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2934</v>
+        <v>-0.2262</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6083</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.848</v>
+        <v>-1.7636</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9954</v>
+        <v>-0.8774</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8526</v>
+        <v>-0.8862</v>
       </c>
       <c r="G11" t="n">
         <v>0.788</v>
@@ -1312,13 +1312,13 @@
         <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4942</v>
+        <v>-0.4099</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3734</v>
+        <v>-0.2555</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1208</v>
+        <v>-0.1544</v>
       </c>
       <c r="V11" t="n">
         <v>-1.214</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3872</v>
+        <v>-1.7742</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5711</v>
+        <v>-2.2605</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1839</v>
+        <v>0.4863</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0478</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1075</v>
+        <v>-0.4944</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7389</v>
+        <v>-0.4283</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3686</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.5625</v>
+        <v>10.3095</v>
       </c>
       <c r="E13" t="n">
-        <v>6.875299999999999</v>
+        <v>7.622499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.687000000000001</v>
+        <v>2.6869</v>
       </c>
       <c r="G13" t="n">
         <v>15.0919</v>
@@ -1468,19 +1468,19 @@
         <v>11.5978</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.1168</v>
+        <v>-6.3697</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.3638</v>
+        <v>-4.6172</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.7526</v>
+        <v>-1.7528</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8919</v>
       </c>
       <c r="W13" t="n">
-        <v>5.3921</v>
+        <v>5.392100000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-7.284000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3532</v>
+        <v>5.6843</v>
       </c>
       <c r="E14" t="n">
-        <v>6.4454</v>
+        <v>7.7428</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.0921</v>
+        <v>-2.0585</v>
       </c>
       <c r="G14" t="n">
         <v>4.9441</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5909</v>
+        <v>0.7402</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.411</v>
+        <v>-0.1136</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8202</v>
+        <v>0.8538</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.304</v>
+        <v>1.1924</v>
       </c>
       <c r="E15" t="n">
         <v>3.3521</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0482</v>
+        <v>-2.1598</v>
       </c>
       <c r="G15" t="n">
         <v>0.7771</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3697</v>
+        <v>1.2582</v>
       </c>
       <c r="T15" t="n">
         <v>0.4525</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9173</v>
+        <v>0.8057</v>
       </c>
       <c r="V15" t="n">
         <v>-2.0026</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0617</v>
+        <v>-0.7348</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9526</v>
+        <v>-0.9651</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8908</v>
+        <v>0.2303</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.3879</v>
+        <v>-0.5441</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.8861</v>
+        <v>-2.7357</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5018</v>
+        <v>2.1916</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.1141</v>
+        <v>0.1433</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.2982</v>
+        <v>-0.9474</v>
       </c>
       <c r="L16" t="n">
-        <v>0.184</v>
+        <v>1.0907</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2738</v>
+        <v>-0.6874</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5879</v>
+        <v>-1.7883</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6859</v>
+        <v>1.1009</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9521</v>
+        <v>0.5052</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7289</v>
+        <v>0.0514</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2232</v>
+        <v>0.4538</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4975</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4975</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. EBOUA</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0421</v>
+        <v>-1.4158</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.167</v>
+        <v>-0.8167</v>
       </c>
       <c r="F17" t="n">
-        <v>0.209</v>
+        <v>-0.5991</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.2824</v>
+        <v>-4.3879</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4693</v>
+        <v>-3.8861</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8131</v>
+        <v>-0.5018</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.617</v>
+        <v>-2.1141</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2283</v>
+        <v>-2.2982</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3887</v>
+        <v>0.184</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6655</v>
+        <v>-2.2738</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.241</v>
+        <v>-1.5879</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5756</v>
+        <v>-0.6859</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7162</v>
+        <v>1.4745</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5375</v>
+        <v>0.9596</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1787</v>
+        <v>0.5149</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>1.4975</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>1.4975</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>P. EBOUA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5889</v>
+        <v>-1.5743</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7292</v>
+        <v>-1.3465</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1402</v>
+        <v>-0.2279</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5441</v>
+        <v>-2.2824</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.7357</v>
+        <v>-1.4693</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1916</v>
+        <v>-0.8131</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1433</v>
+        <v>-1.617</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9474</v>
+        <v>-0.2283</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0907</v>
+        <v>-1.3887</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6874</v>
+        <v>-0.6655</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7883</v>
+        <v>-1.241</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1009</v>
+        <v>0.5756</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>0.651</v>
+        <v>1.0998</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2873</v>
+        <v>0.358</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3637</v>
+        <v>0.7418</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8826</v>
+        <v>-1.8443</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7062</v>
+        <v>-1.541</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8236</v>
+        <v>-0.3033</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8428</v>
+        <v>-1.3233</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4154</v>
+        <v>-3.5316</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2582</v>
+        <v>2.2083</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7997</v>
+        <v>-0.8865</v>
       </c>
       <c r="K19" t="n">
-        <v>0.773</v>
+        <v>-2.2582</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.5727</v>
+        <v>1.3717</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0431</v>
+        <v>-0.4368</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3577</v>
+        <v>-1.2734</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3145</v>
+        <v>0.8366</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0876</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0477</v>
+        <v>0.3372</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4129</v>
+        <v>-0.1727</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6348</v>
+        <v>0.5098</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7594</v>
+        <v>-2.2046</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0242</v>
+        <v>-2.9062</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2647</v>
+        <v>0.7016</v>
       </c>
       <c r="G20" t="n">
         <v>-3.286</v>
@@ -2014,13 +2014,13 @@
         <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4881</v>
+        <v>1.0429</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2794</v>
+        <v>0.3973</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2087</v>
+        <v>0.6456</v>
       </c>
       <c r="V20" t="n">
         <v>-0.4254</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7873</v>
+        <v>-2.2865</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2487</v>
+        <v>-2.9421</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5386</v>
+        <v>0.6556</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3233</v>
+        <v>-0.8428</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.5316</v>
+        <v>0.4154</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2083</v>
+        <v>-1.2582</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8865</v>
+        <v>-0.7997</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.2582</v>
+        <v>0.773</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3717</v>
+        <v>-1.5727</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4368</v>
+        <v>-0.0431</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2734</v>
+        <v>-0.3577</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8366</v>
+        <v>0.3145</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4639</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6058</v>
+        <v>0.6438</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8804</v>
+        <v>0.177</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2746</v>
+        <v>0.4668</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8588</v>
+        <v>-2.3299</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6692</v>
+        <v>-1.9615</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1895</v>
+        <v>-0.3683</v>
       </c>
       <c r="G22" t="n">
         <v>-4.8306</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3066</v>
+        <v>0.8355</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.782</v>
+        <v>-0.0743</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0886</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>3.7527</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.4465</v>
+        <v>-3.2626</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8204</v>
+        <v>-0.2307</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6261</v>
+        <v>-3.0319</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3159</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2182</v>
+        <v>-0.0343</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.2827</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3457</v>
+        <v>0.2484</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,25 +2281,25 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.5625</v>
+        <v>-8.7761</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6148</v>
+        <v>-1.614900000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.9478</v>
+        <v>-7.161300000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-15.0918</v>
       </c>
       <c r="H24" t="n">
-        <v>-25.34689999999999</v>
+        <v>-25.3469</v>
       </c>
       <c r="I24" t="n">
         <v>10.2552</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.1262999999999992</v>
+        <v>-0.1263000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>-8.573700000000001</v>
@@ -2326,16 +2326,16 @@
         <v>8.118600000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>7.1165</v>
+        <v>7.903</v>
       </c>
       <c r="T24" t="n">
-        <v>1.7526</v>
+        <v>1.7525</v>
       </c>
       <c r="U24" t="n">
-        <v>5.3641</v>
+        <v>6.1504</v>
       </c>
       <c r="V24" t="n">
-        <v>1.891799999999999</v>
+        <v>1.8918</v>
       </c>
       <c r="W24" t="n">
         <v>8.3561</v>
